--- a/mappingCorps/ig/FRObservationSocialHistoryLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRObservationSocialHistoryLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMHabitusModeDeVieEntree vers le profil CDA FRCDAHabitusModeDeVie, puis vers le profil FHIR FRObservationSocialHistoryDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMObservationSocialHistory vers le profil CDA FRCDAHabitusModeDeVie, puis vers le profil FHIR FRObservationSocialHistoryDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-habitus-mode-de-vie-entree</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation-social-history</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-habitus-mode-de-vie</t>
   </si>
   <si>
-    <t>FRLMHabitusModeDeVieEntree</t>
+    <t>FRLMObservationSocialHistory</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,91 +118,55 @@
     <t>FRCDAHabitusModeDeVie</t>
   </si>
   <si>
-    <t>FRLMHabitusModeDeVieEntree.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDAHabitusModeDeVie.id</t>
-  </si>
-  <si>
-    <t>FRLMHabitusModeDeVieEntree.code</t>
+    <t>FRLMObservationSocialHistory.header.status</t>
+  </si>
+  <si>
+    <t>FRCDAHabitusModeDeVie.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMObservationSocialHistory.observationDate[x]</t>
+  </si>
+  <si>
+    <t>FRCDAHabitusModeDeVie.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMObservationSocialHistory.type</t>
   </si>
   <si>
     <t>FRCDAHabitusModeDeVie.code</t>
   </si>
   <si>
-    <t>FRLMHabitusModeDeVieEntree.code.precision</t>
-  </si>
-  <si>
-    <t>FRCDAHabitusModeDeVie.code.qualifier</t>
-  </si>
-  <si>
-    <t>FRLMHabitusModeDeVieEntree.code.precision.name</t>
-  </si>
-  <si>
-    <t>FRCDAHabitusModeDeVie.code.qualifier.name</t>
-  </si>
-  <si>
-    <t>FRLMHabitusModeDeVieEntree.code.precision.value</t>
-  </si>
-  <si>
-    <t>FRCDAHabitusModeDeVie.code.qualifier.value</t>
-  </si>
-  <si>
-    <t>FRLMHabitusModeDeVieEntree.description</t>
+    <t>FRLMObservationSocialHistory.result</t>
+  </si>
+  <si>
+    <t>FRCDAHabitusModeDeVie.value</t>
+  </si>
+  <si>
+    <t>FRLMObservationSocialHistory.note</t>
   </si>
   <si>
     <t>FRCDAHabitusModeDeVie.text</t>
   </si>
   <si>
-    <t>FRLMHabitusModeDeVieEntree.statut</t>
-  </si>
-  <si>
-    <t>FRCDAHabitusModeDeVie.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMHabitusModeDeVieEntree.horodatage</t>
-  </si>
-  <si>
-    <t>FRCDAHabitusModeDeVie.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMHabitusModeDeVieEntree.resultat</t>
-  </si>
-  <si>
-    <t>FRCDAHabitusModeDeVie.value</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-social-history-document</t>
   </si>
   <si>
     <t>FRObservationSocialHistoryDocument</t>
   </si>
   <si>
-    <t>FRObservationSocialHistoryDocument.identifier</t>
+    <t>FRObservationSocialHistoryDocument.status</t>
+  </si>
+  <si>
+    <t>FRObservationSocialHistoryDocument.effectiveDateTime</t>
   </si>
   <si>
     <t>FRObservationSocialHistoryDocument.code</t>
   </si>
   <si>
-    <t>FRObservationSocialHistoryDocument.component</t>
-  </si>
-  <si>
-    <t>FRObservationSocialHistoryDocument.component.code</t>
-  </si>
-  <si>
-    <t>FRObservationSocialHistoryDocument.component.value</t>
+    <t>FRObservationSocialHistoryDocument.valueCodeableConcept</t>
   </si>
   <si>
     <t>FRObservationSocialHistoryDocument.note</t>
-  </si>
-  <si>
-    <t>FRObservationSocialHistoryDocument.status</t>
-  </si>
-  <si>
-    <t>FRObservationSocialHistoryDocument.effectiveDateTime</t>
-  </si>
-  <si>
-    <t>FRObservationSocialHistoryDocument.value</t>
   </si>
 </sst>
 </file>
@@ -454,7 +418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -568,58 +532,6 @@
         <v>43</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -628,7 +540,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -650,7 +562,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -659,7 +571,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -667,133 +579,81 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
